--- a/Data/EC/NIT-9007859053.xlsx
+++ b/Data/EC/NIT-9007859053.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99D2C1CE-8F88-41ED-83E2-43AC0A83A0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B43496B2-D107-4FAA-8414-78D39DBB8FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C018D87E-C29D-4596-8E3B-15AA2CF64AF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{94C6B587-6D82-4D09-8A22-304B3ECE5596}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>KAREN MARGARITA ABELLA SALGADO</t>
+  </si>
+  <si>
+    <t>2607</t>
   </si>
   <si>
     <t>2606</t>
@@ -620,22 +623,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63CAF2D0-4C74-03FF-04D0-F274EE5166F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0936845F-BAFD-32F6-126E-C32A0CBD8A06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -644,7 +647,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -657,7 +660,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -986,27 +989,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3D49AD-B37C-4F68-8014-4581CE4A9235}">
-  <dimension ref="B2:J71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F348A756-4C51-4400-B909-2DE294CBB630}">
+  <dimension ref="B2:J72"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1015,7 +1018,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1026,7 +1029,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1037,7 +1040,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1048,10 +1051,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1064,8 +1067,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1080,15 +1083,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2668000</v>
+        <v>2721360</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1096,27 +1099,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1136,16 +1139,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1168,7 +1171,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1194,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1214,7 +1217,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1237,7 +1240,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1260,7 +1263,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +1286,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1306,7 +1309,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1329,7 +1332,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1352,7 +1355,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1375,7 +1378,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1398,7 +1401,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1421,7 +1424,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1444,7 +1447,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1467,7 +1470,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1490,7 +1493,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1513,7 +1516,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1536,7 +1539,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1559,7 +1562,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1582,7 +1585,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1605,7 +1608,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1628,7 +1631,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1651,7 +1654,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1674,7 +1677,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1697,7 +1700,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1720,7 +1723,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1743,7 +1746,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1766,7 +1769,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1789,7 +1792,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1812,7 +1815,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1835,7 +1838,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1858,7 +1861,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1881,7 +1884,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1904,7 +1907,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1927,7 +1930,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1950,7 +1953,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1973,7 +1976,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1999,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2019,7 +2022,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2042,7 +2045,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2065,7 +2068,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +2091,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2111,7 +2114,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2134,7 +2137,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2157,7 +2160,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2180,7 +2183,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2203,7 +2206,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2226,7 +2229,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2249,7 +2252,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2272,43 +2275,55 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B65" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="22" t="s">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F65" s="24">
-        <v>53360</v>
-      </c>
-      <c r="G65" s="24">
-        <v>1334000</v>
-      </c>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-      <c r="J65" s="26"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B70" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="32"/>
-      <c r="H70" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="F65" s="18">
+        <v>53360</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1334000</v>
+      </c>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="20"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="24">
+        <v>53360</v>
+      </c>
+      <c r="G66" s="24">
+        <v>1334000</v>
+      </c>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="26"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="32" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C71" s="32"/>
       <c r="H71" s="1" t="s">
@@ -2317,12 +2332,23 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" s="32"/>
+      <c r="H72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="H72:J72"/>
     <mergeCell ref="H71:J71"/>
-    <mergeCell ref="H70:J70"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
